--- a/models/sovereigns/Chile_Sovereign_Model.xlsx
+++ b/models/sovereigns/Chile_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/chile.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/chile.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Chile_Sovereign_Model.xlsx
+++ b/models/sovereigns/Chile_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/chile.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/chile.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Chile_Sovereign_Model.xlsx
+++ b/models/sovereigns/Chile_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/chile.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/chile.json</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.1322</v>
+        <v>4.0773</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">

--- a/models/sovereigns/Chile_Sovereign_Model.xlsx
+++ b/models/sovereigns/Chile_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/chile.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/chile.json</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
